--- a/artfynd/A 4610-2025 artfynd.xlsx
+++ b/artfynd/A 4610-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1683,6 +1683,327 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128490148</v>
+      </c>
+      <c r="B10" t="n">
+        <v>75139</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>O. Färmansbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>605935</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6672664</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Högstubbe klibbal</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Högstubbe klibbal</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128490147</v>
+      </c>
+      <c r="B11" t="n">
+        <v>75139</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>V. Skarpvreten, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>606033</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6672570</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Vedblotta björk</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Vedblotta björk</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128490149</v>
+      </c>
+      <c r="B12" t="n">
+        <v>75139</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>N. Gäddsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>606752</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6671792</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Högstubbe björk</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Högstubbe björk</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4610-2025 artfynd.xlsx
+++ b/artfynd/A 4610-2025 artfynd.xlsx
@@ -1688,7 +1688,7 @@
         <v>128490148</v>
       </c>
       <c r="B10" t="n">
-        <v>75139</v>
+        <v>75154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128490147</v>
       </c>
       <c r="B11" t="n">
-        <v>75139</v>
+        <v>75154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>128490149</v>
       </c>
       <c r="B12" t="n">
-        <v>75139</v>
+        <v>75154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4610-2025 artfynd.xlsx
+++ b/artfynd/A 4610-2025 artfynd.xlsx
@@ -1688,7 +1688,7 @@
         <v>128490148</v>
       </c>
       <c r="B10" t="n">
-        <v>75154</v>
+        <v>75158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128490147</v>
       </c>
       <c r="B11" t="n">
-        <v>75154</v>
+        <v>75158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>128490149</v>
       </c>
       <c r="B12" t="n">
-        <v>75154</v>
+        <v>75158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4610-2025 artfynd.xlsx
+++ b/artfynd/A 4610-2025 artfynd.xlsx
@@ -1688,7 +1688,7 @@
         <v>128490148</v>
       </c>
       <c r="B10" t="n">
-        <v>75158</v>
+        <v>75160</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128490147</v>
       </c>
       <c r="B11" t="n">
-        <v>75158</v>
+        <v>75160</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>128490149</v>
       </c>
       <c r="B12" t="n">
-        <v>75158</v>
+        <v>75160</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4610-2025 artfynd.xlsx
+++ b/artfynd/A 4610-2025 artfynd.xlsx
@@ -1688,7 +1688,7 @@
         <v>128490148</v>
       </c>
       <c r="B10" t="n">
-        <v>75160</v>
+        <v>75187</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128490147</v>
       </c>
       <c r="B11" t="n">
-        <v>75160</v>
+        <v>75187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>128490149</v>
       </c>
       <c r="B12" t="n">
-        <v>75160</v>
+        <v>75187</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4610-2025 artfynd.xlsx
+++ b/artfynd/A 4610-2025 artfynd.xlsx
@@ -1688,7 +1688,7 @@
         <v>128490148</v>
       </c>
       <c r="B10" t="n">
-        <v>75187</v>
+        <v>75188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128490147</v>
       </c>
       <c r="B11" t="n">
-        <v>75187</v>
+        <v>75188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>128490149</v>
       </c>
       <c r="B12" t="n">
-        <v>75187</v>
+        <v>75188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4610-2025 artfynd.xlsx
+++ b/artfynd/A 4610-2025 artfynd.xlsx
@@ -1688,7 +1688,7 @@
         <v>128490148</v>
       </c>
       <c r="B10" t="n">
-        <v>75188</v>
+        <v>75192</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128490147</v>
       </c>
       <c r="B11" t="n">
-        <v>75188</v>
+        <v>75192</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>128490149</v>
       </c>
       <c r="B12" t="n">
-        <v>75188</v>
+        <v>75192</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4610-2025 artfynd.xlsx
+++ b/artfynd/A 4610-2025 artfynd.xlsx
@@ -1688,7 +1688,7 @@
         <v>128490148</v>
       </c>
       <c r="B10" t="n">
-        <v>75192</v>
+        <v>82988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128490147</v>
       </c>
       <c r="B11" t="n">
-        <v>75192</v>
+        <v>82988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>128490149</v>
       </c>
       <c r="B12" t="n">
-        <v>75192</v>
+        <v>82988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4610-2025 artfynd.xlsx
+++ b/artfynd/A 4610-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55188989</v>
+        <v>70120418</v>
       </c>
       <c r="B2" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordmyran, Upl</t>
+          <t>450 m NV om Norströms, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606170.3327638877</v>
+        <v>606296</v>
       </c>
       <c r="R2" t="n">
-        <v>6672214.141449947</v>
+        <v>6672141</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-05-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-05-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ÅGP-inventering</t>
+          <t>Upplandsfloran - detaljuppgifter.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,36 +761,30 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>död björk</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Lennart Karlén</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55188990</v>
+        <v>128490147</v>
       </c>
       <c r="B3" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,39 +792,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nordmyran, Upl</t>
+          <t>V. Skarpvreten, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606263.9990675867</v>
+        <v>606033</v>
       </c>
       <c r="R3" t="n">
-        <v>6671925.082512476</v>
+        <v>6672570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,27 +846,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-05-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-05-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ÅGP-inventering</t>
+          <t>Vedblotta björk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,35 +868,30 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>död björk</t>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Vedblotta björk</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55188978</v>
+        <v>128490148</v>
       </c>
       <c r="B4" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,39 +899,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101735</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nordmyran, Upl</t>
+          <t>O. Färmansbo, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606079.8630546118</v>
+        <v>605935</v>
       </c>
       <c r="R4" t="n">
-        <v>6672272.760092533</v>
+        <v>6672664</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,27 +953,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-05-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-05-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ÅGP-inventering</t>
+          <t>Högstubbe klibbal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,57 +975,52 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>död björk</t>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Högstubbe klibbal</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55188979</v>
+        <v>55188987</v>
       </c>
       <c r="B5" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6275</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101735</v>
+        <v>101520</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Större flatbagge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Peltis grossa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1101,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606161.3102594841</v>
+        <v>606269</v>
       </c>
       <c r="R5" t="n">
-        <v>6672164.09065262</v>
+        <v>6672325</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,22 +1065,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-05-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-05-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-16</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1186,12 +1110,7 @@
         <v>55188991</v>
       </c>
       <c r="B6" t="n">
-        <v>6203</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6275</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606263.9990675867</v>
+        <v>606264</v>
       </c>
       <c r="R6" t="n">
-        <v>6671925.082512476</v>
+        <v>6671925</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,19 +1180,9 @@
           <t>2015-05-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-05-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1310,37 +1219,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>55188987</v>
+        <v>55188977</v>
       </c>
       <c r="B7" t="n">
-        <v>6203</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101520</v>
+        <v>101735</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större flatbagge</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Peltis grossa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1355,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606268.8541379924</v>
+        <v>606019</v>
       </c>
       <c r="R7" t="n">
-        <v>6672325.039036856</v>
+        <v>6672312</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1385,22 +1289,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-05-16</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-05-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1437,15 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>55188988</v>
+        <v>55188978</v>
       </c>
       <c r="B8" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>606228.9623949546</v>
+        <v>606080</v>
       </c>
       <c r="R8" t="n">
-        <v>6672324.877598052</v>
+        <v>6672273</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1512,22 +1401,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-05-16</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-05-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1564,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>70120418</v>
+        <v>55188979</v>
       </c>
       <c r="B9" t="n">
-        <v>98151</v>
+        <v>44177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,37 +1454,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>569</v>
+        <v>101735</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>450 m NV om Norströms, Upl</t>
+          <t>Nordmyran, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>606296</v>
+        <v>606161</v>
       </c>
       <c r="R9" t="n">
-        <v>6672141</v>
+        <v>6672164</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1629,17 +1513,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>2015-05-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1993-12-31</t>
+          <t>2015-05-14</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>ÅGP-inventering</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1650,30 +1534,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>död björk</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lennart Karlén</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128490148</v>
+        <v>55188980</v>
       </c>
       <c r="B10" t="n">
-        <v>82988</v>
+        <v>44177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,34 +1566,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6439</v>
+        <v>101735</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>O. Färmansbo, Upl</t>
+          <t>Nordmyran, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>605935</v>
+        <v>606142</v>
       </c>
       <c r="R10" t="n">
-        <v>6672664</v>
+        <v>6672063</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1735,17 +1625,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2015-05-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2015-05-14</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Högstubbe klibbal</t>
+          <t>ÅGP-inventering</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1757,30 +1647,30 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Högstubbe klibbal</t>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>död björk</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128490147</v>
+        <v>55188988</v>
       </c>
       <c r="B11" t="n">
-        <v>82988</v>
+        <v>44177</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,34 +1678,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>101735</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>V. Skarpvreten, Upl</t>
+          <t>Nordmyran, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>606033</v>
+        <v>606229</v>
       </c>
       <c r="R11" t="n">
-        <v>6672570</v>
+        <v>6672325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,17 +1737,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2015-05-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2015-05-16</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Vedblotta björk</t>
+          <t>ÅGP-inventering</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1864,30 +1759,30 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Vedblotta björk</t>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>död björk</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128490149</v>
+        <v>55188989</v>
       </c>
       <c r="B12" t="n">
-        <v>82988</v>
+        <v>44177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,34 +1790,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>101735</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N. Gäddsjön, Upl</t>
+          <t>Nordmyran, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>606752</v>
+        <v>606170</v>
       </c>
       <c r="R12" t="n">
-        <v>6671792</v>
+        <v>6672214</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1949,17 +1849,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2015-05-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2015-05-16</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Högstubbe björk</t>
+          <t>ÅGP-inventering</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1971,23 +1871,348 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Högstubbe björk</t>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>död björk</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>55188990</v>
+      </c>
+      <c r="B13" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nordmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>606264</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6671925</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2015-05-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2015-05-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ÅGP-inventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>död björk</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>70121694</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99857</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222308</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rankstarr</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carex elongata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>450 m NV om Norströms, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>606296</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6672141</v>
+      </c>
+      <c r="S14" t="n">
+        <v>100</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1993-01-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1993-12-31</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lennart Karlén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128490149</v>
+      </c>
+      <c r="B15" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>N. Gäddsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>606752</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6671792</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Högstubbe björk</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Högstubbe björk</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Ola Hammarström</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Ola Hammarström</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4610-2025 artfynd.xlsx
+++ b/artfynd/A 4610-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70120418</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128490147</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128490148</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55188987</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55188991</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55188977</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55188978</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55188979</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1664,6 +1709,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55188980</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1776,6 +1826,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55188988</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1888,6 +1943,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55188989</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2000,6 +2060,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55188990</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2106,6 +2171,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70121694</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2213,8 +2283,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128490149</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>